--- a/erp-server/erp-server-wms/src/main/resources/excel/qcNoticeDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/qcNoticeDetailTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -57,7 +57,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>质检通知数量</t>
+      <t>送检数量</t>
     </r>
   </si>
 </sst>
@@ -1047,7 +1047,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>1</formula1>
       <formula2>10000000</formula2>
     </dataValidation>
